--- a/data/predictions/botafogo_valores_previstos.xlsx
+++ b/data/predictions/botafogo_valores_previstos.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30306"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30317"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_1CAD6400D36DCADEE54878D6425DCE3A8746C8A2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED985330-4309-4938-A8D6-64AC61312F3D}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_4B81B4DED44A6ADEE54878D6425DCE3A874654F7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DEECAE44-FAB9-456E-BAD5-66E473016919}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="93">
   <si>
     <t>ano_campeonato</t>
   </si>
@@ -317,7 +317,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -373,7 +373,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -676,11 +676,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V81"/>
+  <dimension ref="A1:V82"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="11" max="11" width="9.28515625" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:22">
       <c r="A1" s="1" t="s">
@@ -6188,6 +6185,65 @@
       </c>
       <c r="V81" t="s">
         <v>26</v>
+      </c>
+    </row>
+    <row r="82" spans="1:22">
+      <c r="A82">
+        <v>2026</v>
+      </c>
+      <c r="B82" t="s">
+        <v>27</v>
+      </c>
+      <c r="C82" t="s">
+        <v>28</v>
+      </c>
+      <c r="D82" s="2">
+        <v>46226</v>
+      </c>
+      <c r="E82" t="s">
+        <v>24</v>
+      </c>
+      <c r="F82" t="s">
+        <v>34</v>
+      </c>
+      <c r="G82">
+        <v>44.529300689697273</v>
+      </c>
+      <c r="H82">
+        <v>0.64775582065073345</v>
+      </c>
+      <c r="I82">
+        <v>19.50216847666842</v>
+      </c>
+      <c r="J82">
+        <v>16.800999969482419</v>
+      </c>
+      <c r="L82">
+        <v>1</v>
+      </c>
+      <c r="M82">
+        <v>0.80833333333333335</v>
+      </c>
+      <c r="N82">
+        <v>0.56666666666666665</v>
+      </c>
+      <c r="P82">
+        <v>1</v>
+      </c>
+      <c r="Q82">
+        <v>0.55833333333333335</v>
+      </c>
+      <c r="R82">
+        <v>0.56666666666666665</v>
+      </c>
+      <c r="T82" t="s">
+        <v>26</v>
+      </c>
+      <c r="U82" t="s">
+        <v>71</v>
+      </c>
+      <c r="V82" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>
